--- a/Models/Молоко/results/Молоко - Результаты прогнозов Prophet средние.xlsx
+++ b/Models/Молоко/results/Молоко - Результаты прогнозов Prophet средние.xlsx
@@ -457,13 +457,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4211.87</v>
+        <v>3276.09</v>
       </c>
       <c r="C2" t="n">
-        <v>4187.99</v>
+        <v>3229.36</v>
       </c>
       <c r="D2" t="n">
-        <v>21.34</v>
+        <v>19.57</v>
       </c>
     </row>
     <row r="3">
@@ -473,13 +473,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2976.4</v>
+        <v>2832.43</v>
       </c>
       <c r="C3" t="n">
-        <v>2863.32</v>
+        <v>2706.96</v>
       </c>
       <c r="D3" t="n">
-        <v>19.02</v>
+        <v>22.16</v>
       </c>
     </row>
     <row r="4">
@@ -489,13 +489,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10870.58</v>
+        <v>6359.82</v>
       </c>
       <c r="C4" t="n">
-        <v>10488.37</v>
+        <v>6164.3</v>
       </c>
       <c r="D4" t="n">
-        <v>39.35</v>
+        <v>25.56</v>
       </c>
     </row>
     <row r="5">
@@ -505,13 +505,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>815.7</v>
+        <v>748.6900000000001</v>
       </c>
       <c r="C5" t="n">
-        <v>777.67</v>
+        <v>689.5</v>
       </c>
       <c r="D5" t="n">
-        <v>27.55</v>
+        <v>27.4</v>
       </c>
     </row>
     <row r="6">
@@ -521,13 +521,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8553.639999999999</v>
+        <v>6824.78</v>
       </c>
       <c r="C6" t="n">
-        <v>8401.110000000001</v>
+        <v>6533.59</v>
       </c>
       <c r="D6" t="n">
-        <v>41.14</v>
+        <v>33.76</v>
       </c>
     </row>
     <row r="7">
@@ -537,13 +537,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15.43</v>
+        <v>17.83</v>
       </c>
       <c r="C7" t="n">
-        <v>11.76</v>
+        <v>14.98</v>
       </c>
       <c r="D7" t="n">
-        <v>37.92</v>
+        <v>54.61</v>
       </c>
     </row>
     <row r="8">
@@ -553,13 +553,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.99</v>
+        <v>3.04</v>
       </c>
       <c r="C8" t="n">
-        <v>5.49</v>
+        <v>2.78</v>
       </c>
       <c r="D8" t="n">
-        <v>65.70999999999999</v>
+        <v>121.66</v>
       </c>
     </row>
     <row r="9">
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>822.96</v>
+        <v>1220.41</v>
       </c>
       <c r="C9" t="n">
-        <v>760.33</v>
+        <v>1157.05</v>
       </c>
       <c r="D9" t="n">
-        <v>12.39</v>
+        <v>18.57</v>
       </c>
     </row>
     <row r="10">
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3090.7</v>
+        <v>2338.18</v>
       </c>
       <c r="C10" t="n">
-        <v>2983.14</v>
+        <v>2193.3</v>
       </c>
       <c r="D10" t="n">
-        <v>14.85</v>
+        <v>12.86</v>
       </c>
     </row>
     <row r="11">
@@ -601,13 +601,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1442.51</v>
+        <v>1781.31</v>
       </c>
       <c r="C11" t="n">
-        <v>1236.89</v>
+        <v>1612.72</v>
       </c>
       <c r="D11" t="n">
-        <v>7.72</v>
+        <v>9.279999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -617,13 +617,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6175.35</v>
+        <v>3966.48</v>
       </c>
       <c r="C12" t="n">
-        <v>5841.15</v>
+        <v>3528.97</v>
       </c>
       <c r="D12" t="n">
-        <v>30.88</v>
+        <v>22.41</v>
       </c>
     </row>
     <row r="13">
@@ -633,13 +633,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3315.62</v>
+        <v>3502.68</v>
       </c>
       <c r="C13" t="n">
-        <v>3147.06</v>
+        <v>3445.87</v>
       </c>
       <c r="D13" t="n">
-        <v>21.97</v>
+        <v>24.89</v>
       </c>
     </row>
     <row r="14">
@@ -649,13 +649,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>530.22</v>
+        <v>806.6900000000001</v>
       </c>
       <c r="C14" t="n">
-        <v>496.56</v>
+        <v>739.61</v>
       </c>
       <c r="D14" t="n">
-        <v>11.75</v>
+        <v>17.88</v>
       </c>
     </row>
     <row r="15">
@@ -679,13 +679,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>15093.12</v>
+        <v>10258.7</v>
       </c>
       <c r="C16" t="n">
-        <v>14026.59</v>
+        <v>8843.110000000001</v>
       </c>
       <c r="D16" t="n">
-        <v>54.33</v>
+        <v>48.84</v>
       </c>
     </row>
     <row r="17">
@@ -695,13 +695,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>6130.52</v>
+        <v>3145.18</v>
       </c>
       <c r="C17" t="n">
-        <v>5591.92</v>
+        <v>2665.94</v>
       </c>
       <c r="D17" t="n">
-        <v>30.42</v>
+        <v>17.73</v>
       </c>
     </row>
     <row r="18">
@@ -711,13 +711,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4082.61</v>
+        <v>3056.43</v>
       </c>
       <c r="C18" t="n">
-        <v>3681.61</v>
+        <v>2366.68</v>
       </c>
       <c r="D18" t="n">
-        <v>69.81</v>
+        <v>46.63</v>
       </c>
     </row>
     <row r="19">
@@ -727,13 +727,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3141.2</v>
+        <v>4618.77</v>
       </c>
       <c r="C19" t="n">
-        <v>3004.66</v>
+        <v>4529.75</v>
       </c>
       <c r="D19" t="n">
-        <v>16.56</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="20">
@@ -743,13 +743,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4480.29</v>
+        <v>5908.14</v>
       </c>
       <c r="C20" t="n">
-        <v>4315.02</v>
+        <v>5666.45</v>
       </c>
       <c r="D20" t="n">
-        <v>16.76</v>
+        <v>23.96</v>
       </c>
     </row>
     <row r="21">
@@ -759,13 +759,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>7278.45</v>
+        <v>3535.36</v>
       </c>
       <c r="C21" t="n">
-        <v>6916.66</v>
+        <v>3119.19</v>
       </c>
       <c r="D21" t="n">
-        <v>17.52</v>
+        <v>8.23</v>
       </c>
     </row>
   </sheetData>
